--- a/resources/templates/standard/L2200-01.xlsx
+++ b/resources/templates/standard/L2200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -562,7 +565,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -577,18 +582,18 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -659,25 +664,25 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -689,26 +694,26 @@
     </row>
     <row r="6" ht="13.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -722,7 +727,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -732,44 +737,44 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T7" s="1"/>
     </row>
